--- a/GenBOE/GenBOE.Tests/Resources/moqtablessc.xlsx
+++ b/GenBOE/GenBOE.Tests/Resources/moqtablessc.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ranzalon\Source\repos\IES\GenBOE\GenBOE.Web\Templates\Export\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twilson3\source\IES\GenBOE\GenBOE.Tests\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAADD539-BEDB-40AA-B034-4F397B15DCC2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275B867D-4C33-4930-B9A0-E53BE3BE4300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{F2BDE59F-50D5-4F91-B73E-5DFBD476F53C}"/>
+    <workbookView xWindow="2805" yWindow="405" windowWidth="19395" windowHeight="15480" xr2:uid="{F2BDE59F-50D5-4F91-B73E-5DFBD476F53C}"/>
   </bookViews>
   <sheets>
     <sheet name="MOQ Tables" sheetId="1" r:id="rId1"/>
     <sheet name="Option Lists" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOQ Tables'!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MOQ Tables'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Table Name</t>
   </si>
@@ -129,9 +129,6 @@
     <t>Employee ID Filters</t>
   </si>
   <si>
-    <t>Total Relevant Hours After Employee ID Filters Applied</t>
-  </si>
-  <si>
     <t>Query Type</t>
   </si>
   <si>
@@ -139,6 +136,12 @@
   </si>
   <si>
     <t>Monthly</t>
+  </si>
+  <si>
+    <t>Period of Performance (PoP): Months</t>
+  </si>
+  <si>
+    <t>Total Relevant Hours exclude unpaid (zero cost) hours and service centers, after application of Employee ID Filters</t>
   </si>
 </sst>
 </file>
@@ -290,7 +293,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="7" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -300,6 +303,9 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="1" xfId="7" applyNumberFormat="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="genBOE" xfId="7" xr:uid="{3E4869EB-5B79-4DE7-855F-A2B8CADB72D2}"/>
@@ -325,9 +331,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -365,7 +371,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -471,7 +477,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -613,7 +619,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -621,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C581C636-3424-4611-9D2C-375716778AB5}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.85546875" style="2" bestFit="1" customWidth="1"/>
@@ -632,12 +638,13 @@
     <col min="6" max="6" width="42" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="42" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="41.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="57.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="60.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.140625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="57.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="60.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.140625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,21 +669,24 @@
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="K1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="F2" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{7D4A90C3-D4CB-40BE-BC1C-2D75CA06857E}"/>
+  <autoFilter ref="A1:K1" xr:uid="{7D4A90C3-D4CB-40BE-BC1C-2D75CA06857E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -710,17 +720,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
